--- a/artfynd/A 55555-2024 artfynd.xlsx
+++ b/artfynd/A 55555-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122885767</v>
+        <v>122885340</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>91300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>233025</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis jelicii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tortič &amp; A.David</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626568</v>
+        <v>626567</v>
       </c>
       <c r="R3" t="n">
-        <v>6706498</v>
+        <v>6706521</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -873,6 +868,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Stark doft. Tunn. Enda jag kommer på. Ska mikroskoperas.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122885340</v>
+        <v>122885517</v>
       </c>
       <c r="B4" t="n">
-        <v>91300</v>
+        <v>98355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,20 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>233025</v>
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis jelicii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tortič &amp; A.David</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626567</v>
+        <v>626573</v>
       </c>
       <c r="R4" t="n">
-        <v>6706521</v>
+        <v>6706498</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,11 +985,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Stark doft. Tunn. Enda jag kommer på. Ska mikroskoperas.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122885517</v>
+        <v>122885767</v>
       </c>
       <c r="B5" t="n">
         <v>98355</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626573</v>
+        <v>626568</v>
       </c>
       <c r="R5" t="n">
         <v>6706498</v>

--- a/artfynd/A 55555-2024 artfynd.xlsx
+++ b/artfynd/A 55555-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122886339</v>
+        <v>122885226</v>
       </c>
       <c r="B2" t="n">
-        <v>95901</v>
+        <v>95903</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626582</v>
+        <v>626549</v>
       </c>
       <c r="R2" t="n">
-        <v>6706488</v>
+        <v>6706535</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122885340</v>
+        <v>122885767</v>
       </c>
       <c r="B3" t="n">
-        <v>91300</v>
+        <v>98357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,20 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>233025</v>
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Skeletocutis jelicii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tortič &amp; A.David</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626567</v>
+        <v>626568</v>
       </c>
       <c r="R3" t="n">
-        <v>6706521</v>
+        <v>6706498</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,11 +873,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Stark doft. Tunn. Enda jag kommer på. Ska mikroskoperas.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>122885517</v>
       </c>
       <c r="B4" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122885767</v>
+        <v>122885340</v>
       </c>
       <c r="B5" t="n">
-        <v>98355</v>
+        <v>91300</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>233025</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis jelicii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tortič &amp; A.David</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626568</v>
+        <v>626567</v>
       </c>
       <c r="R5" t="n">
-        <v>6706498</v>
+        <v>6706521</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1097,6 +1092,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Stark doft. Tunn. Enda jag kommer på. Ska mikroskoperas.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122885226</v>
+        <v>122886339</v>
       </c>
       <c r="B6" t="n">
-        <v>95901</v>
+        <v>95903</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626549</v>
+        <v>626582</v>
       </c>
       <c r="R6" t="n">
-        <v>6706535</v>
+        <v>6706488</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 55555-2024 artfynd.xlsx
+++ b/artfynd/A 55555-2024 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122885340</v>
+        <v>122886339</v>
       </c>
       <c r="B5" t="n">
-        <v>91300</v>
+        <v>95903</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,20 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>233025</v>
+        <v>53</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis jelicii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tortič &amp; A.David</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626567</v>
+        <v>626582</v>
       </c>
       <c r="R5" t="n">
-        <v>6706521</v>
+        <v>6706488</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1081,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Stark doft. Tunn. Enda jag kommer på. Ska mikroskoperas.</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122886339</v>
+        <v>122885340</v>
       </c>
       <c r="B6" t="n">
-        <v>95903</v>
+        <v>91300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
+        <v>233025</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Skeletocutis jelicii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Tortič &amp; A.David</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626582</v>
+        <v>626567</v>
       </c>
       <c r="R6" t="n">
-        <v>6706488</v>
+        <v>6706521</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1203,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stark doft. Tunn. Enda jag kommer på. Ska mikroskoperas.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 55555-2024 artfynd.xlsx
+++ b/artfynd/A 55555-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122885226</v>
+        <v>122885767</v>
       </c>
       <c r="B2" t="n">
-        <v>95903</v>
+        <v>98357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626549</v>
+        <v>626568</v>
       </c>
       <c r="R2" t="n">
-        <v>6706535</v>
+        <v>6706498</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122885767</v>
+        <v>122885226</v>
       </c>
       <c r="B3" t="n">
-        <v>98357</v>
+        <v>95903</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626568</v>
+        <v>626549</v>
       </c>
       <c r="R3" t="n">
-        <v>6706498</v>
+        <v>6706535</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122885517</v>
+        <v>122886339</v>
       </c>
       <c r="B4" t="n">
-        <v>98357</v>
+        <v>95903</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626573</v>
+        <v>626582</v>
       </c>
       <c r="R4" t="n">
-        <v>6706498</v>
+        <v>6706488</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122886339</v>
+        <v>122885517</v>
       </c>
       <c r="B5" t="n">
-        <v>95903</v>
+        <v>98357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626582</v>
+        <v>626573</v>
       </c>
       <c r="R5" t="n">
-        <v>6706488</v>
+        <v>6706498</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 55555-2024 artfynd.xlsx
+++ b/artfynd/A 55555-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122885767</v>
+        <v>122885226</v>
       </c>
       <c r="B2" t="n">
-        <v>98357</v>
+        <v>95911</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626568</v>
+        <v>626549</v>
       </c>
       <c r="R2" t="n">
-        <v>6706498</v>
+        <v>6706535</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122885226</v>
+        <v>122886339</v>
       </c>
       <c r="B3" t="n">
-        <v>95903</v>
+        <v>95911</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626549</v>
+        <v>626582</v>
       </c>
       <c r="R3" t="n">
-        <v>6706535</v>
+        <v>6706488</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122886339</v>
+        <v>122885517</v>
       </c>
       <c r="B4" t="n">
-        <v>95903</v>
+        <v>98365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626582</v>
+        <v>626573</v>
       </c>
       <c r="R4" t="n">
-        <v>6706488</v>
+        <v>6706498</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122885517</v>
+        <v>122885767</v>
       </c>
       <c r="B5" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626573</v>
+        <v>626568</v>
       </c>
       <c r="R5" t="n">
         <v>6706498</v>
@@ -1126,7 +1126,7 @@
         <v>122885340</v>
       </c>
       <c r="B6" t="n">
-        <v>91300</v>
+        <v>91308</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 55555-2024 artfynd.xlsx
+++ b/artfynd/A 55555-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122886339</v>
+        <v>122885767</v>
       </c>
       <c r="B3" t="n">
-        <v>95911</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626582</v>
+        <v>626568</v>
       </c>
       <c r="R3" t="n">
-        <v>6706488</v>
+        <v>6706498</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122885767</v>
+        <v>122886339</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>95911</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626568</v>
+        <v>626582</v>
       </c>
       <c r="R5" t="n">
-        <v>6706498</v>
+        <v>6706488</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 55555-2024 artfynd.xlsx
+++ b/artfynd/A 55555-2024 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122885767</v>
+        <v>122885517</v>
       </c>
       <c r="B3" t="n">
         <v>98365</v>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626568</v>
+        <v>626573</v>
       </c>
       <c r="R3" t="n">
         <v>6706498</v>
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122885517</v>
+        <v>122885767</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626573</v>
+        <v>626568</v>
       </c>
       <c r="R4" t="n">
         <v>6706498</v>

--- a/artfynd/A 55555-2024 artfynd.xlsx
+++ b/artfynd/A 55555-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122885226</v>
+        <v>122886339</v>
       </c>
       <c r="B2" t="n">
         <v>95911</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626549</v>
+        <v>626582</v>
       </c>
       <c r="R2" t="n">
-        <v>6706535</v>
+        <v>6706488</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122885517</v>
+        <v>122885226</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>95911</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626573</v>
+        <v>626549</v>
       </c>
       <c r="R3" t="n">
-        <v>6706498</v>
+        <v>6706535</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122885767</v>
+        <v>122885517</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626568</v>
+        <v>626573</v>
       </c>
       <c r="R4" t="n">
         <v>6706498</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122886339</v>
+        <v>122885767</v>
       </c>
       <c r="B5" t="n">
-        <v>95911</v>
+        <v>98365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626582</v>
+        <v>626568</v>
       </c>
       <c r="R5" t="n">
-        <v>6706488</v>
+        <v>6706498</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 55555-2024 artfynd.xlsx
+++ b/artfynd/A 55555-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122886339</v>
       </c>
       <c r="B2" t="n">
-        <v>95911</v>
+        <v>95914</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122885226</v>
+        <v>122885517</v>
       </c>
       <c r="B3" t="n">
-        <v>95911</v>
+        <v>98368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626549</v>
+        <v>626573</v>
       </c>
       <c r="R3" t="n">
-        <v>6706535</v>
+        <v>6706498</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122885517</v>
+        <v>122885226</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>95914</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626573</v>
+        <v>626549</v>
       </c>
       <c r="R4" t="n">
-        <v>6706498</v>
+        <v>6706535</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
         <v>122885767</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>122885340</v>
       </c>
       <c r="B6" t="n">
-        <v>91308</v>
+        <v>91311</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 55555-2024 artfynd.xlsx
+++ b/artfynd/A 55555-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122886339</v>
+        <v>122885517</v>
       </c>
       <c r="B2" t="n">
-        <v>95914</v>
+        <v>98370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626582</v>
+        <v>626573</v>
       </c>
       <c r="R2" t="n">
-        <v>6706488</v>
+        <v>6706498</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122885517</v>
+        <v>122885226</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>95916</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626573</v>
+        <v>626549</v>
       </c>
       <c r="R3" t="n">
-        <v>6706498</v>
+        <v>6706535</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122885226</v>
+        <v>122885767</v>
       </c>
       <c r="B4" t="n">
-        <v>95914</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626549</v>
+        <v>626568</v>
       </c>
       <c r="R4" t="n">
-        <v>6706535</v>
+        <v>6706498</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122885767</v>
+        <v>122886339</v>
       </c>
       <c r="B5" t="n">
-        <v>98368</v>
+        <v>95916</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626568</v>
+        <v>626582</v>
       </c>
       <c r="R5" t="n">
-        <v>6706498</v>
+        <v>6706488</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,7 +1126,7 @@
         <v>122885340</v>
       </c>
       <c r="B6" t="n">
-        <v>91311</v>
+        <v>91313</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 55555-2024 artfynd.xlsx
+++ b/artfynd/A 55555-2024 artfynd.xlsx
@@ -1152,6 +1152,9 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
@@ -1208,7 +1211,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Stark doft. Tunn. Enda jag kommer på. Ska mikroskoperas.</t>
+          <t>Oklart. Kanske grantickeporing?</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,6 +1220,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55555-2024 artfynd.xlsx
+++ b/artfynd/A 55555-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122885517</v>
+        <v>122885226</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>95922</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626573</v>
+        <v>626549</v>
       </c>
       <c r="R2" t="n">
-        <v>6706498</v>
+        <v>6706535</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122885226</v>
+        <v>122886339</v>
       </c>
       <c r="B3" t="n">
-        <v>95916</v>
+        <v>95922</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626549</v>
+        <v>626582</v>
       </c>
       <c r="R3" t="n">
-        <v>6706535</v>
+        <v>6706488</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>122885767</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122886339</v>
+        <v>122885517</v>
       </c>
       <c r="B5" t="n">
-        <v>95916</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626582</v>
+        <v>626573</v>
       </c>
       <c r="R5" t="n">
-        <v>6706488</v>
+        <v>6706498</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,7 +1126,7 @@
         <v>122885340</v>
       </c>
       <c r="B6" t="n">
-        <v>91313</v>
+        <v>91319</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 55555-2024 artfynd.xlsx
+++ b/artfynd/A 55555-2024 artfynd.xlsx
@@ -1126,7 +1126,7 @@
         <v>122885340</v>
       </c>
       <c r="B6" t="n">
-        <v>91322</v>
+        <v>91339</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 55555-2024 artfynd.xlsx
+++ b/artfynd/A 55555-2024 artfynd.xlsx
@@ -1126,7 +1126,7 @@
         <v>122885340</v>
       </c>
       <c r="B6" t="n">
-        <v>91339</v>
+        <v>91344</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 55555-2024 artfynd.xlsx
+++ b/artfynd/A 55555-2024 artfynd.xlsx
@@ -1126,7 +1126,7 @@
         <v>122885340</v>
       </c>
       <c r="B6" t="n">
-        <v>91344</v>
+        <v>91346</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
